--- a/data/nzd0052/nzd0052.xlsx
+++ b/data/nzd0052/nzd0052.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E518"/>
+  <dimension ref="A1:E524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11310,6 +11310,132 @@
         <v>385.31</v>
       </c>
       <c r="E518" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>378.71</v>
+      </c>
+      <c r="C519" t="n">
+        <v>379.52</v>
+      </c>
+      <c r="D519" t="n">
+        <v>385.79</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>378.91</v>
+      </c>
+      <c r="C520" t="n">
+        <v>379.14</v>
+      </c>
+      <c r="D520" t="n">
+        <v>386.08</v>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>379.34</v>
+      </c>
+      <c r="C521" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="D521" t="n">
+        <v>386.66</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>380.2</v>
+      </c>
+      <c r="C522" t="n">
+        <v>381.32</v>
+      </c>
+      <c r="D522" t="n">
+        <v>388.36</v>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>380.45</v>
+      </c>
+      <c r="C523" t="n">
+        <v>381.75</v>
+      </c>
+      <c r="D523" t="n">
+        <v>388.89</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>380.23</v>
+      </c>
+      <c r="C524" t="n">
+        <v>382.22</v>
+      </c>
+      <c r="D524" t="n">
+        <v>389.2</v>
+      </c>
+      <c r="E524" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11326,7 +11452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17449,6 +17575,66 @@
       </c>
       <c r="B612" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -17617,28 +17803,28 @@
         <v>0.0864</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03209362907067859</v>
+        <v>0.03342052784762084</v>
       </c>
       <c r="J2" t="n">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="K2" t="n">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005559897911511236</v>
+        <v>0.006162826140839406</v>
       </c>
       <c r="M2" t="n">
-        <v>2.592706866234189</v>
+        <v>2.57156550347304</v>
       </c>
       <c r="N2" t="n">
-        <v>11.31126975221744</v>
+        <v>11.19143014524506</v>
       </c>
       <c r="O2" t="n">
-        <v>3.363223119600816</v>
+        <v>3.345359494171749</v>
       </c>
       <c r="P2" t="n">
-        <v>378.1333224542484</v>
+        <v>378.1197822720106</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17695,28 +17881,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1456771564905306</v>
+        <v>0.1374783807140224</v>
       </c>
       <c r="J3" t="n">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="K3" t="n">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09816651510255481</v>
+        <v>0.0889621272036315</v>
       </c>
       <c r="M3" t="n">
-        <v>2.705633088155755</v>
+        <v>2.724089632980376</v>
       </c>
       <c r="N3" t="n">
-        <v>11.97037577265251</v>
+        <v>12.02607051774272</v>
       </c>
       <c r="O3" t="n">
-        <v>3.459823084010584</v>
+        <v>3.467862528668448</v>
       </c>
       <c r="P3" t="n">
-        <v>380.6679125973878</v>
+        <v>380.7514706657043</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17773,28 +17959,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02377648891161131</v>
+        <v>-0.02253684268992585</v>
       </c>
       <c r="J4" t="n">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="K4" t="n">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002991169375655245</v>
+        <v>0.002745664583584273</v>
       </c>
       <c r="M4" t="n">
-        <v>2.714074118246261</v>
+        <v>2.698309165796383</v>
       </c>
       <c r="N4" t="n">
-        <v>11.56951980631742</v>
+        <v>11.46220720567489</v>
       </c>
       <c r="O4" t="n">
-        <v>3.401399683412318</v>
+        <v>3.385588162443106</v>
       </c>
       <c r="P4" t="n">
-        <v>387.5365169306961</v>
+        <v>387.5238515369716</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17832,7 +18018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E518"/>
+  <dimension ref="A1:E524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31821,6 +32007,168 @@
         </is>
       </c>
     </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-35.02046263858249,173.86253730152976</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-35.020883277553224,173.86324640390342</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-35.0211083419394,173.8640755125305</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-35.02046118271684,173.8625385951475</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-35.020886261511926,173.86324435683352</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-35.02110592921196,173.86407673792024</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-35.02045805260565,173.8625413764254</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-35.02088249230093,173.86324694260597</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-35.02110110375702,173.86407918869952</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-35.020451792383085,173.8625469389806</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-35.020869143011545,173.8632561005482</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-35.021086960181925,173.8640863720164</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-35.0204499725509,173.8625485560023</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-35.02086576642649,173.86325841696842</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-35.02108255071431,173.86408861152057</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-35.02045157400323,173.8625471330232</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-35.02086207574042,173.86326094886934</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-35.02107997159173,173.86408992141915</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0052/nzd0052.xlsx
+++ b/data/nzd0052/nzd0052.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E524"/>
+  <dimension ref="A1:E527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11438,6 +11438,69 @@
       <c r="E524" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>380.38</v>
+      </c>
+      <c r="C525" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="D525" t="n">
+        <v>389.95</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>380.53</v>
+      </c>
+      <c r="C526" t="n">
+        <v>383.59</v>
+      </c>
+      <c r="D526" t="n">
+        <v>390.42</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>380.67</v>
+      </c>
+      <c r="C527" t="n">
+        <v>384.12</v>
+      </c>
+      <c r="D527" t="n">
+        <v>390.77</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B618"/>
+  <dimension ref="A1:B621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17635,6 +17698,36 @@
       </c>
       <c r="B618" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -17803,28 +17896,28 @@
         <v>0.0864</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03342052784762084</v>
+        <v>0.03495091784348104</v>
       </c>
       <c r="J2" t="n">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="K2" t="n">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006162826140839406</v>
+        <v>0.006805583380450897</v>
       </c>
       <c r="M2" t="n">
-        <v>2.57156550347304</v>
+        <v>2.56525686107651</v>
       </c>
       <c r="N2" t="n">
-        <v>11.19143014524506</v>
+        <v>11.14038421866231</v>
       </c>
       <c r="O2" t="n">
-        <v>3.345359494171749</v>
+        <v>3.337721411181933</v>
       </c>
       <c r="P2" t="n">
-        <v>378.1197822720106</v>
+        <v>378.104126915342</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17881,28 +17974,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1374783807140224</v>
+        <v>0.1365411129869225</v>
       </c>
       <c r="J3" t="n">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="K3" t="n">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0889621272036315</v>
+        <v>0.08873990803198473</v>
       </c>
       <c r="M3" t="n">
-        <v>2.724089632980376</v>
+        <v>2.714359027032017</v>
       </c>
       <c r="N3" t="n">
-        <v>12.02607051774272</v>
+        <v>11.96366772906925</v>
       </c>
       <c r="O3" t="n">
-        <v>3.467862528668448</v>
+        <v>3.458853528131721</v>
       </c>
       <c r="P3" t="n">
-        <v>380.7514706657043</v>
+        <v>380.7610535363999</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17959,28 +18052,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02253684268992585</v>
+        <v>-0.01901124590499575</v>
       </c>
       <c r="J4" t="n">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="K4" t="n">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002745664583584273</v>
+        <v>0.001966123403603581</v>
       </c>
       <c r="M4" t="n">
-        <v>2.698309165796383</v>
+        <v>2.703017123058454</v>
       </c>
       <c r="N4" t="n">
-        <v>11.46220720567489</v>
+        <v>11.46488644578523</v>
       </c>
       <c r="O4" t="n">
-        <v>3.385588162443106</v>
+        <v>3.385983822434068</v>
       </c>
       <c r="P4" t="n">
-        <v>387.5238515369716</v>
+        <v>387.4877854955773</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18018,7 +18111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E524"/>
+  <dimension ref="A1:E527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32169,6 +32262,87 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-35.02045048210391,173.86254810323624</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-35.02085673602435,173.8632646120448</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-35.021073731778955,173.86409309052826</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-35.02044939020459,173.86254907344923</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-35.02085131778292,173.86326832908995</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-35.02106982149625,173.86409507650305</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-35.020448371098574,173.86254997898135</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-35.020847155945226,173.8632711842113</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-35.02106690958357,173.8640965554203</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0052/nzd0052.xlsx
+++ b/data/nzd0052/nzd0052.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E527"/>
+  <dimension ref="A1:E529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11501,6 +11501,48 @@
       <c r="E527" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>380.49</v>
+      </c>
+      <c r="C528" t="n">
+        <v>385.02</v>
+      </c>
+      <c r="D528" t="n">
+        <v>391.6</v>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>380.43</v>
+      </c>
+      <c r="C529" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="D529" t="n">
+        <v>391.49</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B621"/>
+  <dimension ref="A1:B623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17728,6 +17770,26 @@
       </c>
       <c r="B621" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>-0.53</v>
       </c>
     </row>
   </sheetData>
@@ -17896,28 +17958,28 @@
         <v>0.0864</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03495091784348104</v>
+        <v>0.03590171690377163</v>
       </c>
       <c r="J2" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K2" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006805583380450897</v>
+        <v>0.007227691847873974</v>
       </c>
       <c r="M2" t="n">
-        <v>2.56525686107651</v>
+        <v>2.56071299616057</v>
       </c>
       <c r="N2" t="n">
-        <v>11.14038421866231</v>
+        <v>11.1056305533098</v>
       </c>
       <c r="O2" t="n">
-        <v>3.337721411181933</v>
+        <v>3.332511148264893</v>
       </c>
       <c r="P2" t="n">
-        <v>378.104126915342</v>
+        <v>378.0943663177715</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17974,28 +18036,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1365411129869225</v>
+        <v>0.1369502432161991</v>
       </c>
       <c r="J3" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K3" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08873990803198473</v>
+        <v>0.08983431870566916</v>
       </c>
       <c r="M3" t="n">
-        <v>2.714359027032017</v>
+        <v>2.706101092178705</v>
       </c>
       <c r="N3" t="n">
-        <v>11.96366772906925</v>
+        <v>11.91973368829902</v>
       </c>
       <c r="O3" t="n">
-        <v>3.458853528131721</v>
+        <v>3.45249673255443</v>
       </c>
       <c r="P3" t="n">
-        <v>380.7610535363999</v>
+        <v>380.7568535145284</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18052,28 +18114,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01901124590499575</v>
+        <v>-0.01592467942464701</v>
       </c>
       <c r="J4" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="K4" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001966123403603581</v>
+        <v>0.001381369794788312</v>
       </c>
       <c r="M4" t="n">
-        <v>2.703017123058454</v>
+        <v>2.710195796140213</v>
       </c>
       <c r="N4" t="n">
-        <v>11.46488644578523</v>
+        <v>11.49989472540585</v>
       </c>
       <c r="O4" t="n">
-        <v>3.385983822434068</v>
+        <v>3.391149469635015</v>
       </c>
       <c r="P4" t="n">
-        <v>387.4877854955773</v>
+        <v>387.4560997795667</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18111,7 +18173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E527"/>
+  <dimension ref="A1:E529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32343,6 +32405,60 @@
         </is>
       </c>
     </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-35.020449681377755,173.86254881472578</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-35.02084008867351,173.8632760325299</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-35.021060004190566,173.86410006256656</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-35.020450118137475,173.86254842664056</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-35.02083946047158,173.8632764634915</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-35.02106091936313,173.8640995977641</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
